--- a/data/trans_bre/IP24_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP24_R-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,35; 6,89</t>
+          <t>-11,67; 7,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 13,36</t>
+          <t>-6,6; 13,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,31; 5,05</t>
+          <t>-15,72; 4,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,37; 2,78</t>
+          <t>-12,26; 3,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-40,52; 33,72</t>
+          <t>-40,17; 35,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-27,9; 103,15</t>
+          <t>-30,41; 106,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-49,72; 25,1</t>
+          <t>-51,8; 23,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-56,59; 20,35</t>
+          <t>-57,93; 25,7</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 14,59</t>
+          <t>-6,93; 13,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 7,13</t>
+          <t>-9,79; 8,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 13,47</t>
+          <t>-3,26; 13,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 16,51</t>
+          <t>-2,64; 15,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-23,21; 94,62</t>
+          <t>-28,14; 90,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-51,4; 56,26</t>
+          <t>-48,51; 67,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-17,03; 106,32</t>
+          <t>-18,56; 105,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-13,17; 188,35</t>
+          <t>-18,41; 180,04</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,58; 13,11</t>
+          <t>-7,66; 14,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 17,06</t>
+          <t>-2,7; 16,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 20,09</t>
+          <t>-0,55; 20,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,29; 13,92</t>
+          <t>-11,17; 12,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-33,29; 87,02</t>
+          <t>-31,51; 94,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-13,53; 144,62</t>
+          <t>-13,76; 143,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 219,8</t>
+          <t>-5,35; 205,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-57,17; 158,64</t>
+          <t>-59,6; 147,48</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 9,48</t>
+          <t>-4,46; 9,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 11,13</t>
+          <t>-0,57; 11,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 12,7</t>
+          <t>0,78; 12,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,73; 38,03</t>
+          <t>4,56; 41,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-17,15; 47,6</t>
+          <t>-16,81; 48,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 79,5</t>
+          <t>-5,77; 86,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 109,16</t>
+          <t>4,44; 104,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,03; 210,85</t>
+          <t>18,82; 221,76</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,53; 19,33</t>
+          <t>0,13; 19,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 12,24</t>
+          <t>-2,85; 12,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 11,72</t>
+          <t>-2,27; 12,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-21,89; 3,35</t>
+          <t>-25,72; 3,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,19; 111,79</t>
+          <t>1,27; 107,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,35; 102,26</t>
+          <t>-15,46; 101,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 102,7</t>
+          <t>-12,15; 110,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-63,3; 21,79</t>
+          <t>-66,11; 23,39</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-21,2; 1,88</t>
+          <t>-19,69; 0,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 16,41</t>
+          <t>-6,21; 16,42</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,86; 27,84</t>
+          <t>3,77; 28,3</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 16,77</t>
+          <t>-5,56; 16,88</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-56,41; 9,94</t>
+          <t>-55,17; 7,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-32,31; 144,46</t>
+          <t>-34,13; 143,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,98; 219,09</t>
+          <t>10,97; 217,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-32,38; 200,68</t>
+          <t>-34,68; 205,23</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 6,03</t>
+          <t>-1,42; 6,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 7,5</t>
+          <t>0,77; 7,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,99; 9,26</t>
+          <t>2,05; 8,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 17,4</t>
+          <t>-0,33; 15,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 29,76</t>
+          <t>-5,88; 29,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,14; 51,7</t>
+          <t>4,07; 50,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,74; 60,36</t>
+          <t>11,11; 56,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 98,33</t>
+          <t>-2,82; 88,63</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP24_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP24_R-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 7,18</t>
+          <t>-11,7; 7,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 13,14</t>
+          <t>-5,55; 12,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,72; 4,37</t>
+          <t>-14,01; 5,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,26; 3,04</t>
+          <t>-12,04; 3,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-40,17; 35,76</t>
+          <t>-37,67; 35,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-30,41; 106,77</t>
+          <t>-26,26; 98,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-51,8; 23,11</t>
+          <t>-50,59; 24,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-57,93; 25,7</t>
+          <t>-57,95; 26,83</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 13,79</t>
+          <t>-6,29; 13,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,79; 8,03</t>
+          <t>-9,03; 7,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 13,16</t>
+          <t>-3,4; 13,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 15,35</t>
+          <t>-2,62; 15,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-28,14; 90,22</t>
+          <t>-26,4; 86,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-48,51; 67,95</t>
+          <t>-45,22; 65,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-18,56; 105,04</t>
+          <t>-17,91; 109,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-18,41; 180,04</t>
+          <t>-18,59; 175,79</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 14,02</t>
+          <t>-7,78; 13,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 16,51</t>
+          <t>-4,23; 15,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 20,2</t>
+          <t>-0,77; 20,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,17; 12,83</t>
+          <t>-11,09; 13,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-31,51; 94,97</t>
+          <t>-32,54; 81,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-13,76; 143,03</t>
+          <t>-18,76; 139,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 205,67</t>
+          <t>-6,33; 215,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-59,6; 147,48</t>
+          <t>-54,65; 154,56</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 9,36</t>
+          <t>-3,36; 10,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 11,47</t>
+          <t>-1,38; 11,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 12,29</t>
+          <t>1,01; 12,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,56; 41,25</t>
+          <t>5,22; 41,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-16,81; 48,61</t>
+          <t>-12,73; 55,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 86,55</t>
+          <t>-8,16; 83,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,44; 104,85</t>
+          <t>3,95; 106,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,82; 221,76</t>
+          <t>22,32; 247,99</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,13; 19,35</t>
+          <t>1,19; 20,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 12,18</t>
+          <t>-3,49; 12,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 12,11</t>
+          <t>-3,0; 12,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-25,72; 3,59</t>
+          <t>-22,25; 4,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,27; 107,39</t>
+          <t>2,9; 114,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,46; 101,39</t>
+          <t>-16,48; 103,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 110,43</t>
+          <t>-15,64; 103,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-66,11; 23,39</t>
+          <t>-65,01; 27,47</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-19,69; 0,87</t>
+          <t>-21,64; 1,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 16,42</t>
+          <t>-6,3; 16,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,77; 28,3</t>
+          <t>4,29; 29,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 16,88</t>
+          <t>-5,69; 16,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-55,17; 7,43</t>
+          <t>-59,42; 5,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-34,13; 143,66</t>
+          <t>-33,43; 145,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,97; 217,3</t>
+          <t>13,91; 226,81</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-34,68; 205,23</t>
+          <t>-34,55; 213,08</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 6,31</t>
+          <t>-1,47; 5,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 7,44</t>
+          <t>0,84; 7,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,05; 8,65</t>
+          <t>1,81; 8,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 15,71</t>
+          <t>-0,05; 15,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 29,35</t>
+          <t>-5,58; 27,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,07; 50,26</t>
+          <t>4,44; 54,17</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,11; 56,92</t>
+          <t>9,58; 60,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 88,63</t>
+          <t>-1,42; 94,3</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP24_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP24_R-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-4,55</t>
+          <t>-5,1</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-25,93%</t>
+          <t>-29,13%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,7; 7,25</t>
+          <t>-12,35; 6,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 12,55</t>
+          <t>-5,87; 13,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,01; 5,22</t>
+          <t>-14,31; 5,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,04; 3,34</t>
+          <t>-12,73; 2,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-37,67; 35,76</t>
+          <t>-40,52; 33,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-26,26; 98,0</t>
+          <t>-27,9; 103,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-50,59; 24,55</t>
+          <t>-49,72; 25,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-57,95; 26,83</t>
+          <t>-58,57; 18,91</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,62</t>
+          <t>6,7</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>55,67%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 13,78</t>
+          <t>-5,08; 14,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 7,47</t>
+          <t>-10,89; 7,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 13,47</t>
+          <t>-3,23; 13,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 15,06</t>
+          <t>-1,64; 15,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-26,4; 86,48</t>
+          <t>-23,21; 94,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-45,22; 65,06</t>
+          <t>-51,4; 56,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-17,91; 109,42</t>
+          <t>-17,03; 106,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-18,59; 175,79</t>
+          <t>-11,12; 197,84</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,57</t>
+          <t>3,92</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>35,74%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 13,17</t>
+          <t>-7,58; 13,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 15,81</t>
+          <t>-2,15; 17,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 20,19</t>
+          <t>-1,23; 20,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 13,72</t>
+          <t>-6,3; 14,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-32,54; 81,47</t>
+          <t>-33,29; 87,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,76; 139,96</t>
+          <t>-13,53; 144,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 215,32</t>
+          <t>-12,93; 219,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-54,65; 154,56</t>
+          <t>-44,66; 232,84</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17,14</t>
+          <t>5,17</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>27,03%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 10,47</t>
+          <t>-4,06; 9,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 11,54</t>
+          <t>-1,01; 11,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 12,58</t>
+          <t>0,56; 12,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,22; 41,58</t>
+          <t>-1,22; 13,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-12,73; 55,99</t>
+          <t>-17,15; 47,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 83,35</t>
+          <t>-6,6; 79,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,95; 106,82</t>
+          <t>1,91; 109,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22,32; 247,99</t>
+          <t>-6,59; 81,05</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-5,97</t>
+          <t>-5,02</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-27,03%</t>
+          <t>-25,34%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 20,55</t>
+          <t>1,53; 19,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 12,42</t>
+          <t>-2,92; 12,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 12,03</t>
+          <t>-3,06; 11,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-22,25; 4,03</t>
+          <t>-19,41; 3,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,9; 114,64</t>
+          <t>4,19; 111,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,48; 103,61</t>
+          <t>-17,35; 102,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-15,64; 103,33</t>
+          <t>-17,1; 102,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-65,01; 27,47</t>
+          <t>-62,56; 25,86</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5,3</t>
+          <t>3,0</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>24,55%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-21,64; 1,05</t>
+          <t>-21,2; 1,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 16,33</t>
+          <t>-5,9; 16,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,29; 29,19</t>
+          <t>3,86; 27,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 16,58</t>
+          <t>-6,87; 11,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-59,42; 5,22</t>
+          <t>-56,41; 9,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-33,43; 145,13</t>
+          <t>-32,31; 144,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,91; 226,81</t>
+          <t>15,98; 219,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-34,55; 213,08</t>
+          <t>-41,41; 151,92</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,35</t>
+          <t>1,1</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 5,88</t>
+          <t>-1,43; 6,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,84; 7,9</t>
+          <t>0,48; 7,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,81; 8,98</t>
+          <t>1,99; 9,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 15,15</t>
+          <t>-3,28; 4,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 27,65</t>
+          <t>-5,72; 29,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,44; 54,17</t>
+          <t>3,14; 51,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,58; 60,13</t>
+          <t>10,74; 60,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 94,3</t>
+          <t>-16,91; 31,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP24_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP24_R-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-1,84</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3,81</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-4,89</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-5,1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-7,32%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>22,46%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-19,59%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-29,13%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-1.841976608700396</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>3.810091596046894</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-4.88825667378108</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-5.104424856801688</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.07320549554567017</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.2245895797726441</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.1959375044383936</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.2912837525150944</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-12,35; 6,89</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-5,87; 13,36</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-14,31; 5,05</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-12,73; 2,2</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-40,52; 33,72</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-27,9; 103,15</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-49,72; 25,1</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-58,57; 18,91</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-12.35278695555269</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-5.872663267591518</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-14.31162859896756</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-12.73082453353142</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.4052090548401491</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.2789692724149835</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.4972379962115252</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.5857321136733569</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>6.893966987431045</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>13.36043329125141</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>5.049505415029935</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>2.198026471250436</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.3371592497032434</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1.031537798444303</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.2509904371985674</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.189123496064036</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>3,63</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,88</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>4,8</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6,7</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>17,91%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-5,38%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>28,7%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>55,67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-5,08; 14,59</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-10,89; 7,13</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-3,23; 13,47</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-1,64; 15,79</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-23,21; 94,62</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-51,4; 56,26</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-17,03; 106,32</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-11,12; 197,84</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>3.627977803198077</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.8820911248244856</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>4.801925829868972</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>6.696009045552421</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.1791150672511671</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.0537523552167563</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.2870125478185497</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.5567127570305944</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2,91</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>6,57</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>9,59</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,92</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>14,41%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>40,46%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>68,4%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>35,74%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-5.080517359937649</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-10.88793467996133</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-3.231049605114657</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-1.636943013611435</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.2320762759889346</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.5140458730798891</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.1703216832488039</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.1112478267627989</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-7,58; 13,11</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-2,15; 17,06</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-1,23; 20,09</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-6,3; 14,45</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-33,29; 87,02</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-13,53; 144,62</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-12,93; 219,8</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-44,66; 232,84</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>14.59382670467935</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>7.130349550918173</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>13.4716649906718</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>15.78937768087918</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.9462244414647163</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.5625832555862175</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>1.063150007958604</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>1.978386631674785</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +819,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>2,74</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5,06</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6,7</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5,17</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>12,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>30,86%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>46,18%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>27,03%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>2.911511672134048</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>6.566493722723424</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>9.594588723502294</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>3.916667857894863</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.1441356417941918</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.4045718734529597</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.6840360057349405</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.3574407728486282</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-4,06; 9,48</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-1,01; 11,13</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,56; 12,7</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-1,22; 13,07</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-17,15; 47,6</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-6,6; 79,5</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1,91; 109,16</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-6,59; 81,05</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-7.584214892821373</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-2.146467186184295</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-1.23228073155503</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-6.297568713766847</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.3328717379513502</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.1353307171908121</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.1293297922343327</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.4465524774080593</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>13.11002911419821</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>17.06492503963909</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>20.0852698514611</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>14.44933388797447</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.8702377928137714</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1.446193395684008</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>2.198029613442877</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>2.328445601687612</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>10,78</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>4,67</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>4,75</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-5,02</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>50,08%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>29,37%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>31,96%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-25,34%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>1,53; 19,33</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-2,92; 12,24</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-3,06; 11,72</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-19,41; 3,65</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>4,19; 111,79</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-17,35; 102,26</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-17,1; 102,7</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-62,56; 25,86</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>2.735462322438434</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>5.059325289717412</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>6.703589387009948</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>5.170181972665783</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.1200078851523064</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.3086496140040023</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.4617927717826313</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.2703187447390225</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-9,57</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>4,73</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>16,6</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3,0</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-31,44%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>30,29%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>92,14%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>24,55%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-4.062099424759662</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-1.006390681109589</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.5595902551089992</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-1.223708912143558</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.1715227107647822</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.06601592553674521</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>0.01912499654602007</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.06587847916167368</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-21,2; 1,88</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-5,9; 16,41</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>3,86; 27,84</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-6,87; 11,8</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-56,41; 9,94</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-32,31; 144,46</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>15,98; 219,09</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-41,41; 151,92</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>9.482562112919027</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>11.13335746841787</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>12.6989422249638</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>13.07166486366491</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.4759694322685128</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.7950145080072559</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>1.091590829041285</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.8105124788843791</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +1019,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>2,25</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>4,16</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5,56</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,1</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9,76%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>25,58%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>33,29%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>6,62%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>10.77853049850528</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>4.669404913257785</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>4.750912728070681</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-5.021417747167209</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.5007795612949004</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.2937488901430099</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.3195920292207975</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.2534031330123924</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-1,43; 6,03</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>0,48; 7,5</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1,99; 9,26</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-3,28; 4,83</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-5,72; 29,76</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>3,14; 51,7</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>10,74; 60,36</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-16,91; 31,97</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>1.534191764169536</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.919641103737612</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-3.060641032636168</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-19.41017467874468</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>0.04193393734277692</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.1734830717994194</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.1709888111103736</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.6256151967779132</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>19.33376714240436</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>12.23867115979416</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>11.72212501815046</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>3.652728729081916</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>1.117893216472381</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1.022590028317272</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>1.027024077101774</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.2585668383906158</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-9.573576280874063</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>4.733148572469201</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>16.60186764546405</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>2.99873513641933</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.3143685143631738</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.3028814724373699</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>0.9214371294618459</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>0.245505007655335</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-21.19544074760226</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-5.898042293692004</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>3.863553869194282</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-6.865634334210667</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.5641053596471156</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.3230561369490158</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>0.1598408005945302</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>-0.4140782055196529</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>1.88101975775317</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>16.40964927329391</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>27.83594653260885</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>11.79987958006908</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.09937189049668982</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1.444599843634321</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>2.190936069869305</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>1.519206791633916</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>2.245187685410937</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>4.161072098278732</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>5.55527429865098</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>1.104593639440102</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0.09757735253919986</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>0.255759620326314</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>0.332910986312224</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>0.06618748285412437</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-1.429300915991343</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>0.4821826147123776</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>1.9918926811292</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-3.279855291580758</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.05724219672946121</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>0.03136245730779699</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>0.1074244875699848</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.1690792714968043</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>6.032242675752249</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>7.495998763913196</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>9.259788192204562</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>4.828924588121812</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.2975974513897198</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.5169621239504155</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.6035658804153246</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.3196719012050387</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1317,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
